--- a/artfynd/A 62133-2025 artfynd.xlsx
+++ b/artfynd/A 62133-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,6 +1118,297 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133646270</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83181</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>787352</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7248447</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133646057</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97995</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>787086</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7248737</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133646355</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93206</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>787515</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7248394</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62133-2025 artfynd.xlsx
+++ b/artfynd/A 62133-2025 artfynd.xlsx
@@ -1123,7 +1123,7 @@
         <v>133646270</v>
       </c>
       <c r="B6" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>133646057</v>
       </c>
       <c r="B7" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>133646355</v>
       </c>
       <c r="B8" t="n">
-        <v>93206</v>
+        <v>93208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62133-2025 artfynd.xlsx
+++ b/artfynd/A 62133-2025 artfynd.xlsx
@@ -1123,7 +1123,7 @@
         <v>133646270</v>
       </c>
       <c r="B6" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>133646057</v>
       </c>
       <c r="B7" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>133646355</v>
       </c>
       <c r="B8" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62133-2025 artfynd.xlsx
+++ b/artfynd/A 62133-2025 artfynd.xlsx
@@ -1123,7 +1123,7 @@
         <v>133646270</v>
       </c>
       <c r="B6" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>133646057</v>
       </c>
       <c r="B7" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>133646355</v>
       </c>
       <c r="B8" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62133-2025 artfynd.xlsx
+++ b/artfynd/A 62133-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130081469</v>
+        <v>133646270</v>
       </c>
       <c r="B2" t="n">
-        <v>58198</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787222</v>
+        <v>787352</v>
       </c>
       <c r="R2" t="n">
-        <v>7248516</v>
+        <v>7248447</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>05:14</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>05:14</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +757,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -792,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130081530</v>
+        <v>133646355</v>
       </c>
       <c r="B3" t="n">
-        <v>58506</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788620</v>
+        <v>787515</v>
       </c>
       <c r="R3" t="n">
-        <v>7248090</v>
+        <v>7248394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>02:47</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>02:47</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +854,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -909,57 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133247985</v>
+        <v>133645907</v>
       </c>
       <c r="B4" t="n">
-        <v>58410</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>787252</v>
+        <v>787301</v>
       </c>
       <c r="R4" t="n">
-        <v>7248519</v>
+        <v>7248501</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1120,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133646270</v>
+        <v>133419441</v>
       </c>
       <c r="B6" t="n">
-        <v>83215</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,34 +1082,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787352</v>
+        <v>787240</v>
       </c>
       <c r="R6" t="n">
-        <v>7248447</v>
+        <v>7248566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,12 +1144,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skalad liggande gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,60 +1169,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133646057</v>
+        <v>133247985</v>
       </c>
       <c r="B7" t="n">
-        <v>98053</v>
+        <v>58410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787086</v>
+        <v>787252</v>
       </c>
       <c r="R7" t="n">
-        <v>7248737</v>
+        <v>7248519</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133646355</v>
+        <v>130081469</v>
       </c>
       <c r="B8" t="n">
-        <v>93264</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1325,34 +1298,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>787515</v>
+        <v>787222</v>
       </c>
       <c r="R8" t="n">
-        <v>7248394</v>
+        <v>7248516</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,12 +1361,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,6 +1388,7 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1408,6 +1401,317 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133645784</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>787185</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7248523</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130081530</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>788620</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7248090</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133646057</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>787086</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7248737</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62133-2025 artfynd.xlsx
+++ b/artfynd/A 62133-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133247985</v>
+        <v>134156383</v>
       </c>
       <c r="B7" t="n">
-        <v>58410</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,46 +1192,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787252</v>
+        <v>787088</v>
       </c>
       <c r="R7" t="n">
-        <v>7248519</v>
+        <v>7248765</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,27 +1286,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130081469</v>
+        <v>134156397</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1315,29 +1314,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>787222</v>
+        <v>787090</v>
       </c>
       <c r="R8" t="n">
-        <v>7248516</v>
+        <v>7248784</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,22 +1359,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>05:14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>05:14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,26 +1376,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133645784</v>
+        <v>134158276</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,37 +1402,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>787185</v>
+        <v>787360</v>
       </c>
       <c r="R9" t="n">
-        <v>7248523</v>
+        <v>7248411</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,12 +1464,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,44 +1484,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130081530</v>
+        <v>133247985</v>
       </c>
       <c r="B10" t="n">
-        <v>58636</v>
+        <v>58410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1541,17 +1536,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788620</v>
+        <v>787252</v>
       </c>
       <c r="R10" t="n">
-        <v>7248090</v>
+        <v>7248519</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1575,22 +1570,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>02:47</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>02:47</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,26 +1587,25 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133646057</v>
+        <v>130081469</v>
       </c>
       <c r="B11" t="n">
-        <v>98060</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1613,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>787086</v>
+        <v>787222</v>
       </c>
       <c r="R11" t="n">
-        <v>7248737</v>
+        <v>7248516</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,12 +1676,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,6 +1703,7 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1712,6 +1716,317 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133645784</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>787185</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7248523</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130081530</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>788620</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7248090</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133646057</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>787086</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7248737</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62133-2025 artfynd.xlsx
+++ b/artfynd/A 62133-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646270</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646355</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645907</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133248244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133419441</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134156383</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134156397</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158276</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133247985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130081469</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645784</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646057</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,8 +2092,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130081530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>